--- a/archivos/VAN y TIR.xlsx
+++ b/archivos/VAN y TIR.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
   <si>
     <t>Ingresos Previstos</t>
   </si>
@@ -207,9 +207,6 @@
     <t xml:space="preserve"> CF =</t>
   </si>
   <si>
-    <t>Suponemos que de forma habitual un cliente pequeño consume alrededor de 3 hs mensuales gracias a los buenos y tecnológicos sistemas que LocalTech Tiene</t>
-  </si>
-  <si>
     <t>Costo x hs</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t>Cantidad de clientes</t>
   </si>
   <si>
-    <t>*Aquí no contabilizamos los honorarios, que serán parte de nuestro equipos que presten servicios para LocalTech, es una estrategia que desarrollaremos, en ciertas ramas, se prefiere el trabajo independiente.</t>
-  </si>
-  <si>
     <t>Suponiendo que aspiramos a conseguir aproximadamente 70 clientes acorde a la capacidad según  sueldos y honorarios</t>
   </si>
   <si>
@@ -251,6 +245,15 @@
   <si>
     <t>*Todos los numeros expuestos, son solo a modo de ejemplo. Usted deberá ingresar los de su organización.</t>
   </si>
+  <si>
+    <t>Suponemos que de forma habitual un cliente pequeño consume alrededor de 3 hs mensuales gracias a los buenos y tecnológicos sistemas que la Empresa X Tiene</t>
+  </si>
+  <si>
+    <t>*Aquí no contabilizamos los honorarios, que serán parte de nuestro equipos que presten servicios para Empresa X, es una estrategia que desarrollaremos, en ciertas ramas, se prefiere el trabajo independiente.</t>
+  </si>
+  <si>
+    <t>Ejemplo Empresa X</t>
+  </si>
 </sst>
 </file>
 
@@ -260,7 +263,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,6 +460,14 @@
       <i/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -913,7 +924,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1164,6 +1175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="20% - Énfasis2" xfId="8" builtinId="34"/>
@@ -12496,7 +12508,7 @@
     </row>
     <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="127" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.35">
@@ -13686,7 +13698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:F32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -13697,14 +13709,19 @@
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="136" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="105">
         <v>500000</v>
@@ -13712,7 +13729,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="104">
         <f>8*20</f>
@@ -13721,7 +13738,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="103">
         <f>B4/B5</f>
@@ -13730,7 +13747,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="132" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="132"/>
@@ -13748,21 +13765,21 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="111" t="s">
+      <c r="C10" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="112" t="s">
-        <v>69</v>
-      </c>
       <c r="D10" s="134" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E10" s="134"/>
       <c r="F10" s="134"/>
@@ -13797,14 +13814,14 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="115" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B14" s="114"/>
       <c r="C14" s="114"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="135" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="135"/>
       <c r="C15" s="135"/>
@@ -13814,7 +13831,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -13880,7 +13897,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="92" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -13991,6 +14008,6 @@
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>